--- a/public/2025League.xlsx
+++ b/public/2025League.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17fe194b0d499b50/Desktop/Tennis/toronto-tennis-league/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{0790962C-C37E-4EAD-A29D-006B6287D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CE2014D-A8CC-4F7B-B173-DD0B28892845}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="8_{0790962C-C37E-4EAD-A29D-006B6287D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE68E6F4-3587-47AB-A25B-263192DD1F7E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4A9C3D40-FDBC-41E5-8D07-AF019402ABDD}"/>
+    <workbookView minimized="1" xWindow="1725" yWindow="1725" windowWidth="8910" windowHeight="585" xr2:uid="{4A9C3D40-FDBC-41E5-8D07-AF019402ABDD}"/>
   </bookViews>
   <sheets>
     <sheet name="Men's" sheetId="1" r:id="rId1"/>
@@ -297,6 +297,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,7 +620,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BD46787-79AD-43CC-9306-04447F05B807}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -675,7 +678,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1">
+    <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -721,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>55</v>
       </c>
@@ -813,7 +816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -859,7 +862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1">
+    <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -905,7 +908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>56</v>
       </c>
@@ -951,7 +954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1">
+    <row r="8" spans="1:13">
       <c r="B8" t="s">
         <v>10</v>
       </c>
@@ -994,7 +997,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1">
+    <row r="9" spans="1:13">
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -1037,7 +1040,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1">
+    <row r="10" spans="1:13">
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -1080,7 +1083,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1126,7 +1129,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1">
+    <row r="12" spans="1:13">
       <c r="B12" t="s">
         <v>10</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1">
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,7 +1216,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1">
+    <row r="14" spans="1:13">
       <c r="B14" t="s">
         <v>10</v>
       </c>
@@ -1301,7 +1304,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1">
+    <row r="16" spans="1:13">
       <c r="B16" t="s">
         <v>10</v>
       </c>
@@ -1344,7 +1347,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1">
+    <row r="17" spans="1:13">
       <c r="B17" t="s">
         <v>10</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -1433,7 +1436,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1">
+    <row r="19" spans="1:13">
       <c r="B19" t="s">
         <v>10</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1">
+    <row r="20" spans="1:13">
       <c r="B20" t="s">
         <v>10</v>
       </c>
@@ -1517,7 +1520,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1">
+    <row r="21" spans="1:13">
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
@@ -1564,17 +1567,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M21" xr:uid="{9BD46787-79AD-43CC-9306-04447F05B807}">
-    <filterColumn colId="0">
-      <filters blank="1"/>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Gustavo Linardi Espinosa"/>
-        <filter val="John Lescano"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M21" xr:uid="{9BD46787-79AD-43CC-9306-04447F05B807}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L23">
     <sortCondition descending="1" ref="L1:L23"/>
   </sortState>

--- a/public/2025League.xlsx
+++ b/public/2025League.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/17fe194b0d499b50/Desktop/Tennis/toronto-tennis-league/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="8_{0790962C-C37E-4EAD-A29D-006B6287D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE68E6F4-3587-47AB-A25B-263192DD1F7E}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{0790962C-C37E-4EAD-A29D-006B6287D132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE9FC73F-4ED5-4216-B659-B86178CDA8E2}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1725" yWindow="1725" windowWidth="8910" windowHeight="585" xr2:uid="{4A9C3D40-FDBC-41E5-8D07-AF019402ABDD}"/>
+    <workbookView xWindow="-28920" yWindow="-1185" windowWidth="29040" windowHeight="15720" xr2:uid="{4A9C3D40-FDBC-41E5-8D07-AF019402ABDD}"/>
   </bookViews>
   <sheets>
     <sheet name="Men's" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="65">
   <si>
     <t>user_id</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>1hbwwbdt7ZRjd4dPlWC292lUVFg2</t>
+  </si>
+  <si>
+    <t>ETM78tiMlGWpYtZHgK6w3AiMf103</t>
+  </si>
+  <si>
+    <t>yvNOgObSFqTMmhlrMNrBcAa4mf93</t>
   </si>
 </sst>
 </file>
@@ -998,6 +1004,9 @@
       </c>
     </row>
     <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
@@ -1437,6 +1446,9 @@
       </c>
     </row>
     <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
